--- a/Trimixxx_inputs_list.xlsx
+++ b/Trimixxx_inputs_list.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00344DA6-AB5B-6F46-89A6-CB8AE10CBBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3880" yWindow="660" windowWidth="30680" windowHeight="19920" xr2:uid="{927C92DB-4FA9-6B4F-93BC-15C32ED8A8B9}"/>
+    <workbookView xWindow="3880" yWindow="660" windowWidth="30680" windowHeight="19880" xr2:uid="{927C92DB-4FA9-6B4F-93BC-15C32ED8A8B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
